--- a/Ammoniak/Ammoniak_Brownfield_H2_N2_HB_Pipeline_Höchst/Datenbank.xlsx
+++ b/Ammoniak/Ammoniak_Brownfield_H2_N2_HB_Pipeline_Höchst/Datenbank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Ammoniak\Ammoniak_Brownfield_H2_N2_HB_Pipeline_Höchst\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9FBF47-FD60-4558-BB44-399E26643191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1E50EA-742C-45CD-B53B-99C9E4742025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -144,7 +144,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="333">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -1139,6 +1139,12 @@
   </si>
   <si>
     <t>eta_h2pipe</t>
+  </si>
+  <si>
+    <t>calc_lcoh_h2pipe</t>
+  </si>
+  <si>
+    <t>Levelized Cost of Compression</t>
   </si>
 </sst>
 </file>
@@ -1334,7 +1340,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1417,6 +1423,8 @@
     <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1462,17 +1470,35 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1483,56 +1509,37 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1891,10 +1898,10 @@
       <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="74" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="83" t="s">
+      <c r="B2" s="85" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1911,8 +1918,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="73"/>
-      <c r="B3" s="84"/>
+      <c r="A3" s="75"/>
+      <c r="B3" s="86"/>
       <c r="C3" t="s">
         <v>102</v>
       </c>
@@ -1927,8 +1934,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="73"/>
-      <c r="B4" s="84"/>
+      <c r="A4" s="75"/>
+      <c r="B4" s="86"/>
       <c r="C4" t="s">
         <v>12</v>
       </c>
@@ -1943,8 +1950,8 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="73"/>
-      <c r="B5" s="84"/>
+      <c r="A5" s="75"/>
+      <c r="B5" s="86"/>
       <c r="C5" t="s">
         <v>13</v>
       </c>
@@ -1959,8 +1966,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="73"/>
-      <c r="B6" s="84"/>
+      <c r="A6" s="75"/>
+      <c r="B6" s="86"/>
       <c r="C6" t="s">
         <v>15</v>
       </c>
@@ -1975,8 +1982,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="73"/>
-      <c r="B7" s="84"/>
+      <c r="A7" s="75"/>
+      <c r="B7" s="86"/>
       <c r="C7" t="s">
         <v>17</v>
       </c>
@@ -1991,8 +1998,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="73"/>
-      <c r="B8" s="85" t="s">
+      <c r="A8" s="75"/>
+      <c r="B8" s="87" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -2009,8 +2016,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="73"/>
-      <c r="B9" s="84"/>
+      <c r="A9" s="75"/>
+      <c r="B9" s="86"/>
       <c r="C9" t="s">
         <v>105</v>
       </c>
@@ -2025,8 +2032,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="73"/>
-      <c r="B10" s="84"/>
+      <c r="A10" s="75"/>
+      <c r="B10" s="86"/>
       <c r="C10" t="s">
         <v>12</v>
       </c>
@@ -2041,8 +2048,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="73"/>
-      <c r="B11" s="84"/>
+      <c r="A11" s="75"/>
+      <c r="B11" s="86"/>
       <c r="C11" t="s">
         <v>13</v>
       </c>
@@ -2058,8 +2065,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="73"/>
-      <c r="B12" s="84"/>
+      <c r="A12" s="75"/>
+      <c r="B12" s="86"/>
       <c r="C12" t="s">
         <v>110</v>
       </c>
@@ -2074,8 +2081,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="73"/>
-      <c r="B13" s="84"/>
+      <c r="A13" s="75"/>
+      <c r="B13" s="86"/>
       <c r="C13" t="s">
         <v>109</v>
       </c>
@@ -2090,8 +2097,8 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="73"/>
-      <c r="B14" s="84"/>
+      <c r="A14" s="75"/>
+      <c r="B14" s="86"/>
       <c r="C14" t="s">
         <v>15</v>
       </c>
@@ -2106,8 +2113,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="73"/>
-      <c r="B15" s="86"/>
+      <c r="A15" s="75"/>
+      <c r="B15" s="88"/>
       <c r="C15" s="5" t="s">
         <v>17</v>
       </c>
@@ -2122,8 +2129,8 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="73"/>
-      <c r="B16" s="78" t="s">
+      <c r="A16" s="75"/>
+      <c r="B16" s="80" t="s">
         <v>4</v>
       </c>
       <c r="C16" s="4" t="s">
@@ -2141,8 +2148,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="73"/>
-      <c r="B17" s="105"/>
+      <c r="A17" s="75"/>
+      <c r="B17" s="90"/>
       <c r="C17" s="50" t="s">
         <v>12</v>
       </c>
@@ -2157,8 +2164,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="73"/>
-      <c r="B18" s="105"/>
+      <c r="A18" s="75"/>
+      <c r="B18" s="90"/>
       <c r="C18" s="50" t="s">
         <v>13</v>
       </c>
@@ -2173,8 +2180,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="73"/>
-      <c r="B19" s="105"/>
+      <c r="A19" s="75"/>
+      <c r="B19" s="90"/>
       <c r="C19" s="50" t="s">
         <v>15</v>
       </c>
@@ -2189,8 +2196,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="73"/>
-      <c r="B20" s="79"/>
+      <c r="A20" s="75"/>
+      <c r="B20" s="81"/>
       <c r="C20" s="5" t="s">
         <v>17</v>
       </c>
@@ -2205,8 +2212,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="73"/>
-      <c r="B21" s="106" t="s">
+      <c r="A21" s="75"/>
+      <c r="B21" s="89" t="s">
         <v>310</v>
       </c>
       <c r="C21" t="s">
@@ -2223,8 +2230,8 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="73"/>
-      <c r="B22" s="106"/>
+      <c r="A22" s="75"/>
+      <c r="B22" s="89"/>
       <c r="C22" t="s">
         <v>12</v>
       </c>
@@ -2239,8 +2246,8 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="73"/>
-      <c r="B23" s="106"/>
+      <c r="A23" s="75"/>
+      <c r="B23" s="89"/>
       <c r="C23" t="s">
         <v>13</v>
       </c>
@@ -2255,8 +2262,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="73"/>
-      <c r="B24" s="106"/>
+      <c r="A24" s="75"/>
+      <c r="B24" s="89"/>
       <c r="C24" t="s">
         <v>329</v>
       </c>
@@ -2271,8 +2278,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="73"/>
-      <c r="B25" s="106"/>
+      <c r="A25" s="75"/>
+      <c r="B25" s="89"/>
       <c r="C25" t="s">
         <v>15</v>
       </c>
@@ -2287,8 +2294,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="73"/>
-      <c r="B26" s="106"/>
+      <c r="A26" s="75"/>
+      <c r="B26" s="89"/>
       <c r="C26" t="s">
         <v>17</v>
       </c>
@@ -2303,10 +2310,10 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="72" t="s">
+      <c r="A27" s="74" t="s">
         <v>85</v>
       </c>
-      <c r="B27" s="76" t="s">
+      <c r="B27" s="78" t="s">
         <v>5</v>
       </c>
       <c r="C27" s="2" t="s">
@@ -2323,8 +2330,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="73"/>
-      <c r="B28" s="77"/>
+      <c r="A28" s="75"/>
+      <c r="B28" s="79"/>
       <c r="C28" t="s">
         <v>13</v>
       </c>
@@ -2339,8 +2346,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="73"/>
-      <c r="B29" s="77"/>
+      <c r="A29" s="75"/>
+      <c r="B29" s="79"/>
       <c r="C29" t="s">
         <v>15</v>
       </c>
@@ -2355,8 +2362,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="73"/>
-      <c r="B30" s="77"/>
+      <c r="A30" s="75"/>
+      <c r="B30" s="79"/>
       <c r="C30" t="s">
         <v>22</v>
       </c>
@@ -2371,8 +2378,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="73"/>
-      <c r="B31" s="77"/>
+      <c r="A31" s="75"/>
+      <c r="B31" s="79"/>
       <c r="C31" t="s">
         <v>47</v>
       </c>
@@ -2387,8 +2394,8 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="73"/>
-      <c r="B32" s="77"/>
+      <c r="A32" s="75"/>
+      <c r="B32" s="79"/>
       <c r="C32" t="s">
         <v>48</v>
       </c>
@@ -2403,8 +2410,8 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="73"/>
-      <c r="B33" s="77"/>
+      <c r="A33" s="75"/>
+      <c r="B33" s="79"/>
       <c r="C33" t="s">
         <v>17</v>
       </c>
@@ -2419,8 +2426,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="73"/>
-      <c r="B34" s="77"/>
+      <c r="A34" s="75"/>
+      <c r="B34" s="79"/>
       <c r="C34" t="s">
         <v>114</v>
       </c>
@@ -2435,8 +2442,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="73"/>
-      <c r="B35" s="78" t="s">
+      <c r="A35" s="75"/>
+      <c r="B35" s="80" t="s">
         <v>258</v>
       </c>
       <c r="C35" s="4" t="s">
@@ -2453,8 +2460,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="73"/>
-      <c r="B36" s="81"/>
+      <c r="A36" s="75"/>
+      <c r="B36" s="83"/>
       <c r="C36" s="50" t="s">
         <v>23</v>
       </c>
@@ -2470,8 +2477,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="73"/>
-      <c r="B37" s="81"/>
+      <c r="A37" s="75"/>
+      <c r="B37" s="83"/>
       <c r="C37" s="50" t="s">
         <v>18</v>
       </c>
@@ -2486,8 +2493,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="73"/>
-      <c r="B38" s="81"/>
+      <c r="A38" s="75"/>
+      <c r="B38" s="83"/>
       <c r="C38" s="50" t="s">
         <v>19</v>
       </c>
@@ -2502,8 +2509,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="73"/>
-      <c r="B39" s="81"/>
+      <c r="A39" s="75"/>
+      <c r="B39" s="83"/>
       <c r="C39" s="50" t="s">
         <v>47</v>
       </c>
@@ -2518,8 +2525,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="73"/>
-      <c r="B40" s="81"/>
+      <c r="A40" s="75"/>
+      <c r="B40" s="83"/>
       <c r="C40" s="50" t="s">
         <v>48</v>
       </c>
@@ -2534,8 +2541,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="73"/>
-      <c r="B41" s="81"/>
+      <c r="A41" s="75"/>
+      <c r="B41" s="83"/>
       <c r="C41" s="50" t="s">
         <v>115</v>
       </c>
@@ -2550,8 +2557,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="73"/>
-      <c r="B42" s="81"/>
+      <c r="A42" s="75"/>
+      <c r="B42" s="83"/>
       <c r="C42" s="50" t="s">
         <v>114</v>
       </c>
@@ -2566,8 +2573,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="73"/>
-      <c r="B43" s="81"/>
+      <c r="A43" s="75"/>
+      <c r="B43" s="83"/>
       <c r="C43" s="50" t="s">
         <v>15</v>
       </c>
@@ -2582,8 +2589,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="74"/>
-      <c r="B44" s="82"/>
+      <c r="A44" s="76"/>
+      <c r="B44" s="84"/>
       <c r="C44" s="14" t="s">
         <v>17</v>
       </c>
@@ -2598,7 +2605,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="72" t="s">
+      <c r="A45" s="74" t="s">
         <v>86</v>
       </c>
       <c r="B45" s="56" t="s">
@@ -2618,7 +2625,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="75"/>
+      <c r="A46" s="77"/>
       <c r="B46" s="66" t="s">
         <v>302</v>
       </c>
@@ -2636,7 +2643,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="75"/>
+      <c r="A47" s="77"/>
       <c r="B47" s="59" t="s">
         <v>299</v>
       </c>
@@ -2654,8 +2661,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="73"/>
-      <c r="B48" s="78" t="s">
+      <c r="A48" s="75"/>
+      <c r="B48" s="80" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="4" t="s">
@@ -2672,8 +2679,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="73"/>
-      <c r="B49" s="77"/>
+      <c r="A49" s="75"/>
+      <c r="B49" s="79"/>
       <c r="C49" t="s">
         <v>12</v>
       </c>
@@ -2688,8 +2695,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="73"/>
-      <c r="B50" s="77"/>
+      <c r="A50" s="75"/>
+      <c r="B50" s="79"/>
       <c r="C50" t="s">
         <v>19</v>
       </c>
@@ -2704,8 +2711,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="73"/>
-      <c r="B51" s="77"/>
+      <c r="A51" s="75"/>
+      <c r="B51" s="79"/>
       <c r="C51" t="s">
         <v>20</v>
       </c>
@@ -2720,8 +2727,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="73"/>
-      <c r="B52" s="77"/>
+      <c r="A52" s="75"/>
+      <c r="B52" s="79"/>
       <c r="C52" t="s">
         <v>15</v>
       </c>
@@ -2736,8 +2743,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="73"/>
-      <c r="B53" s="77"/>
+      <c r="A53" s="75"/>
+      <c r="B53" s="79"/>
       <c r="C53" t="s">
         <v>82</v>
       </c>
@@ -2752,8 +2759,8 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="73"/>
-      <c r="B54" s="79"/>
+      <c r="A54" s="75"/>
+      <c r="B54" s="81"/>
       <c r="C54" s="5" t="s">
         <v>17</v>
       </c>
@@ -2768,8 +2775,8 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="73"/>
-      <c r="B55" s="78" t="s">
+      <c r="A55" s="75"/>
+      <c r="B55" s="80" t="s">
         <v>7</v>
       </c>
       <c r="C55" s="4" t="s">
@@ -2786,8 +2793,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="73"/>
-      <c r="B56" s="77"/>
+      <c r="A56" s="75"/>
+      <c r="B56" s="79"/>
       <c r="C56" t="s">
         <v>12</v>
       </c>
@@ -2802,8 +2809,8 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="73"/>
-      <c r="B57" s="77"/>
+      <c r="A57" s="75"/>
+      <c r="B57" s="79"/>
       <c r="C57" t="s">
         <v>19</v>
       </c>
@@ -2818,8 +2825,8 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="73"/>
-      <c r="B58" s="77"/>
+      <c r="A58" s="75"/>
+      <c r="B58" s="79"/>
       <c r="C58" t="s">
         <v>20</v>
       </c>
@@ -2834,8 +2841,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="73"/>
-      <c r="B59" s="77"/>
+      <c r="A59" s="75"/>
+      <c r="B59" s="79"/>
       <c r="C59" t="s">
         <v>15</v>
       </c>
@@ -2850,8 +2857,8 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="73"/>
-      <c r="B60" s="77"/>
+      <c r="A60" s="75"/>
+      <c r="B60" s="79"/>
       <c r="C60" t="s">
         <v>82</v>
       </c>
@@ -2866,8 +2873,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="74"/>
-      <c r="B61" s="80"/>
+      <c r="A61" s="76"/>
+      <c r="B61" s="82"/>
       <c r="C61" s="14" t="s">
         <v>17</v>
       </c>
@@ -2882,7 +2889,7 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="72" t="s">
+      <c r="A62" s="74" t="s">
         <v>90</v>
       </c>
       <c r="B62" s="16" t="s">
@@ -2902,7 +2909,7 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="73"/>
+      <c r="A63" s="75"/>
       <c r="B63" s="17" t="s">
         <v>93</v>
       </c>
@@ -2920,7 +2927,7 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="74"/>
+      <c r="A64" s="76"/>
       <c r="B64" s="1" t="s">
         <v>94</v>
       </c>
@@ -2960,7 +2967,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
-  <dimension ref="A1:F127"/>
+  <dimension ref="A1:F128"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" style="12" customWidth="1"/>
@@ -2993,10 +3000,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="91" t="s">
+      <c r="A2" s="99" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="94" t="s">
+      <c r="B2" s="103" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="27" t="s">
@@ -3011,8 +3018,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="93"/>
-      <c r="B3" s="88"/>
+      <c r="A3" s="101"/>
+      <c r="B3" s="105"/>
       <c r="C3" s="12" t="s">
         <v>136</v>
       </c>
@@ -3025,8 +3032,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="93"/>
-      <c r="B4" s="88"/>
+      <c r="A4" s="101"/>
+      <c r="B4" s="105"/>
       <c r="C4" s="12" t="s">
         <v>102</v>
       </c>
@@ -3039,8 +3046,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="93"/>
-      <c r="B5" s="88"/>
+      <c r="A5" s="101"/>
+      <c r="B5" s="105"/>
       <c r="C5" s="12" t="s">
         <v>172</v>
       </c>
@@ -3053,8 +3060,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="93"/>
-      <c r="B6" s="88"/>
+      <c r="A6" s="101"/>
+      <c r="B6" s="105"/>
       <c r="C6" s="12" t="s">
         <v>184</v>
       </c>
@@ -3067,8 +3074,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="93"/>
-      <c r="B7" s="88"/>
+      <c r="A7" s="101"/>
+      <c r="B7" s="105"/>
       <c r="C7" s="12" t="s">
         <v>202</v>
       </c>
@@ -3081,8 +3088,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="93"/>
-      <c r="B8" s="88"/>
+      <c r="A8" s="101"/>
+      <c r="B8" s="105"/>
       <c r="C8" s="12" t="s">
         <v>251</v>
       </c>
@@ -3095,8 +3102,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="93"/>
-      <c r="B9" s="88"/>
+      <c r="A9" s="101"/>
+      <c r="B9" s="105"/>
       <c r="C9" s="12" t="s">
         <v>216</v>
       </c>
@@ -3109,8 +3116,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="93"/>
-      <c r="B10" s="88"/>
+      <c r="A10" s="101"/>
+      <c r="B10" s="105"/>
       <c r="C10" s="12" t="s">
         <v>241</v>
       </c>
@@ -3123,13 +3130,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="93"/>
-      <c r="B11" s="88"/>
+      <c r="A11" s="101"/>
+      <c r="B11" s="105"/>
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="93"/>
-      <c r="B12" s="87" t="s">
+      <c r="A12" s="101"/>
+      <c r="B12" s="107" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="36" t="s">
@@ -3144,8 +3151,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="93"/>
-      <c r="B13" s="88"/>
+      <c r="A13" s="101"/>
+      <c r="B13" s="105"/>
       <c r="C13" s="12" t="s">
         <v>177</v>
       </c>
@@ -3158,8 +3165,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="93"/>
-      <c r="B14" s="88"/>
+      <c r="A14" s="101"/>
+      <c r="B14" s="105"/>
       <c r="C14" s="12" t="s">
         <v>180</v>
       </c>
@@ -3172,8 +3179,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="93"/>
-      <c r="B15" s="88"/>
+      <c r="A15" s="101"/>
+      <c r="B15" s="105"/>
       <c r="C15" s="12" t="s">
         <v>181</v>
       </c>
@@ -3186,8 +3193,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="93"/>
-      <c r="B16" s="88"/>
+      <c r="A16" s="101"/>
+      <c r="B16" s="105"/>
       <c r="C16" s="12" t="s">
         <v>102</v>
       </c>
@@ -3200,8 +3207,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="93"/>
-      <c r="B17" s="88"/>
+      <c r="A17" s="101"/>
+      <c r="B17" s="105"/>
       <c r="C17" s="12" t="s">
         <v>184</v>
       </c>
@@ -3214,8 +3221,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="93"/>
-      <c r="B18" s="88"/>
+      <c r="A18" s="101"/>
+      <c r="B18" s="105"/>
       <c r="C18" s="12" t="s">
         <v>202</v>
       </c>
@@ -3228,8 +3235,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="93"/>
-      <c r="B19" s="88"/>
+      <c r="A19" s="101"/>
+      <c r="B19" s="105"/>
       <c r="C19" s="12" t="s">
         <v>251</v>
       </c>
@@ -3242,8 +3249,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="93"/>
-      <c r="B20" s="88"/>
+      <c r="A20" s="101"/>
+      <c r="B20" s="105"/>
       <c r="C20" s="12" t="s">
         <v>216</v>
       </c>
@@ -3256,8 +3263,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="93"/>
-      <c r="B21" s="88"/>
+      <c r="A21" s="101"/>
+      <c r="B21" s="105"/>
       <c r="C21" s="12" t="s">
         <v>241</v>
       </c>
@@ -3270,16 +3277,16 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="93"/>
-      <c r="B22" s="90"/>
+      <c r="A22" s="101"/>
+      <c r="B22" s="106"/>
       <c r="C22" s="38"/>
       <c r="D22" s="38"/>
       <c r="E22" s="39"/>
       <c r="F22" s="38"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="93"/>
-      <c r="B23" s="98" t="s">
+      <c r="A23" s="101"/>
+      <c r="B23" s="91" t="s">
         <v>4</v>
       </c>
       <c r="C23" s="36" t="s">
@@ -3294,22 +3301,22 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="93"/>
-      <c r="B24" s="107"/>
+      <c r="A24" s="101"/>
+      <c r="B24" s="92"/>
       <c r="C24" s="54" t="s">
         <v>136</v>
       </c>
       <c r="D24" s="54" t="s">
         <v>145</v>
       </c>
-      <c r="E24" s="108"/>
+      <c r="E24" s="72"/>
       <c r="F24" s="54" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="93"/>
-      <c r="B25" s="107"/>
+      <c r="A25" s="101"/>
+      <c r="B25" s="92"/>
       <c r="C25" s="54" t="s">
         <v>102</v>
       </c>
@@ -3322,64 +3329,64 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="93"/>
-      <c r="B26" s="107"/>
+      <c r="A26" s="101"/>
+      <c r="B26" s="92"/>
       <c r="C26" s="54" t="s">
         <v>174</v>
       </c>
       <c r="D26" s="54" t="s">
         <v>173</v>
       </c>
-      <c r="E26" s="109"/>
+      <c r="E26" s="73"/>
       <c r="F26" s="54" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="93"/>
-      <c r="B27" s="107"/>
+      <c r="A27" s="101"/>
+      <c r="B27" s="92"/>
       <c r="C27" s="54" t="s">
         <v>184</v>
       </c>
       <c r="D27" s="54" t="s">
         <v>189</v>
       </c>
-      <c r="E27" s="109"/>
+      <c r="E27" s="73"/>
       <c r="F27" s="54" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="93"/>
-      <c r="B28" s="107"/>
+      <c r="A28" s="101"/>
+      <c r="B28" s="92"/>
       <c r="C28" s="54" t="s">
         <v>202</v>
       </c>
       <c r="D28" s="54" t="s">
         <v>206</v>
       </c>
-      <c r="E28" s="109"/>
+      <c r="E28" s="73"/>
       <c r="F28" s="54" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="93"/>
-      <c r="B29" s="107"/>
+      <c r="A29" s="101"/>
+      <c r="B29" s="92"/>
       <c r="C29" s="54" t="s">
         <v>251</v>
       </c>
       <c r="D29" s="54" t="s">
         <v>254</v>
       </c>
-      <c r="E29" s="109"/>
+      <c r="E29" s="73"/>
       <c r="F29" s="54" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="93"/>
-      <c r="B30" s="107"/>
+      <c r="A30" s="101"/>
+      <c r="B30" s="92"/>
       <c r="C30" s="54" t="s">
         <v>216</v>
       </c>
@@ -3392,8 +3399,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="93"/>
-      <c r="B31" s="107"/>
+      <c r="A31" s="101"/>
+      <c r="B31" s="92"/>
       <c r="C31" s="54" t="s">
         <v>241</v>
       </c>
@@ -3406,16 +3413,16 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="93"/>
-      <c r="B32" s="103"/>
+      <c r="A32" s="101"/>
+      <c r="B32" s="93"/>
       <c r="C32" s="38"/>
       <c r="D32" s="38"/>
       <c r="E32" s="39"/>
       <c r="F32" s="38"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="93"/>
-      <c r="B33" s="110" t="s">
+      <c r="A33" s="101"/>
+      <c r="B33" s="108" t="s">
         <v>310</v>
       </c>
       <c r="C33" s="12" t="s">
@@ -3430,8 +3437,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="93"/>
-      <c r="B34" s="106"/>
+      <c r="A34" s="101"/>
+      <c r="B34" s="89"/>
       <c r="C34" s="12" t="s">
         <v>136</v>
       </c>
@@ -3444,8 +3451,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="93"/>
-      <c r="B35" s="106"/>
+      <c r="A35" s="101"/>
+      <c r="B35" s="89"/>
       <c r="C35" s="12" t="s">
         <v>102</v>
       </c>
@@ -3458,8 +3465,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="93"/>
-      <c r="B36" s="106"/>
+      <c r="A36" s="101"/>
+      <c r="B36" s="89"/>
       <c r="C36" s="12" t="s">
         <v>180</v>
       </c>
@@ -3472,8 +3479,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="93"/>
-      <c r="B37" s="106"/>
+      <c r="A37" s="101"/>
+      <c r="B37" s="89"/>
       <c r="C37" s="12" t="s">
         <v>327</v>
       </c>
@@ -3486,8 +3493,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="93"/>
-      <c r="B38" s="106"/>
+      <c r="A38" s="101"/>
+      <c r="B38" s="89"/>
       <c r="C38" s="12" t="s">
         <v>184</v>
       </c>
@@ -3500,8 +3507,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="93"/>
-      <c r="B39" s="106"/>
+      <c r="A39" s="101"/>
+      <c r="B39" s="89"/>
       <c r="C39" s="12" t="s">
         <v>202</v>
       </c>
@@ -3514,8 +3521,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="93"/>
-      <c r="B40" s="106"/>
+      <c r="A40" s="101"/>
+      <c r="B40" s="89"/>
       <c r="C40" s="12" t="s">
         <v>251</v>
       </c>
@@ -3528,8 +3535,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="93"/>
-      <c r="B41" s="106"/>
+      <c r="A41" s="101"/>
+      <c r="B41" s="89"/>
       <c r="C41" s="12" t="s">
         <v>216</v>
       </c>
@@ -3542,8 +3549,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="93"/>
-      <c r="B42" s="106"/>
+      <c r="A42" s="101"/>
+      <c r="B42" s="89"/>
       <c r="C42" s="12" t="s">
         <v>241</v>
       </c>
@@ -3556,15 +3563,15 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="93"/>
-      <c r="B43" s="111"/>
+      <c r="A43" s="101"/>
+      <c r="B43" s="109"/>
       <c r="E43" s="34"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="91" t="s">
+      <c r="A44" s="99" t="s">
         <v>85</v>
       </c>
-      <c r="B44" s="97" t="s">
+      <c r="B44" s="110" t="s">
         <v>5</v>
       </c>
       <c r="C44" s="27" t="s">
@@ -3579,8 +3586,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="93"/>
-      <c r="B45" s="95"/>
+      <c r="A45" s="101"/>
+      <c r="B45" s="97"/>
       <c r="C45" s="12" t="s">
         <v>140</v>
       </c>
@@ -3593,8 +3600,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="93"/>
-      <c r="B46" s="95"/>
+      <c r="A46" s="101"/>
+      <c r="B46" s="97"/>
       <c r="C46" s="12" t="s">
         <v>169</v>
       </c>
@@ -3607,8 +3614,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="93"/>
-      <c r="B47" s="95"/>
+      <c r="A47" s="101"/>
+      <c r="B47" s="97"/>
       <c r="C47" s="12" t="s">
         <v>170</v>
       </c>
@@ -3621,8 +3628,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="93"/>
-      <c r="B48" s="95"/>
+      <c r="A48" s="101"/>
+      <c r="B48" s="97"/>
       <c r="C48" s="12" t="s">
         <v>184</v>
       </c>
@@ -3635,8 +3642,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="93"/>
-      <c r="B49" s="95"/>
+      <c r="A49" s="101"/>
+      <c r="B49" s="97"/>
       <c r="C49" s="12" t="s">
         <v>202</v>
       </c>
@@ -3649,8 +3656,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="93"/>
-      <c r="B50" s="95"/>
+      <c r="A50" s="101"/>
+      <c r="B50" s="97"/>
       <c r="C50" s="12" t="s">
         <v>251</v>
       </c>
@@ -3663,8 +3670,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="93"/>
-      <c r="B51" s="95"/>
+      <c r="A51" s="101"/>
+      <c r="B51" s="97"/>
       <c r="C51" s="12" t="s">
         <v>216</v>
       </c>
@@ -3677,8 +3684,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="93"/>
-      <c r="B52" s="95"/>
+      <c r="A52" s="101"/>
+      <c r="B52" s="97"/>
       <c r="C52" s="12" t="s">
         <v>241</v>
       </c>
@@ -3691,13 +3698,13 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="93"/>
-      <c r="B53" s="95"/>
+      <c r="A53" s="101"/>
+      <c r="B53" s="97"/>
       <c r="E53" s="34"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="93"/>
-      <c r="B54" s="98" t="s">
+      <c r="A54" s="101"/>
+      <c r="B54" s="91" t="s">
         <v>8</v>
       </c>
       <c r="C54" s="36" t="s">
@@ -3712,8 +3719,8 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="93"/>
-      <c r="B55" s="95"/>
+      <c r="A55" s="101"/>
+      <c r="B55" s="97"/>
       <c r="C55" s="12" t="s">
         <v>142</v>
       </c>
@@ -3726,8 +3733,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="93"/>
-      <c r="B56" s="88"/>
+      <c r="A56" s="101"/>
+      <c r="B56" s="105"/>
       <c r="C56" s="12" t="s">
         <v>140</v>
       </c>
@@ -3740,8 +3747,8 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="93"/>
-      <c r="B57" s="88"/>
+      <c r="A57" s="101"/>
+      <c r="B57" s="105"/>
       <c r="C57" s="12" t="s">
         <v>136</v>
       </c>
@@ -3754,8 +3761,8 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="93"/>
-      <c r="B58" s="88"/>
+      <c r="A58" s="101"/>
+      <c r="B58" s="105"/>
       <c r="C58" s="12" t="s">
         <v>157</v>
       </c>
@@ -3768,8 +3775,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="93"/>
-      <c r="B59" s="88"/>
+      <c r="A59" s="101"/>
+      <c r="B59" s="105"/>
       <c r="C59" s="12" t="s">
         <v>158</v>
       </c>
@@ -3782,8 +3789,8 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="93"/>
-      <c r="B60" s="88"/>
+      <c r="A60" s="101"/>
+      <c r="B60" s="105"/>
       <c r="C60" s="12" t="s">
         <v>184</v>
       </c>
@@ -3796,8 +3803,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="93"/>
-      <c r="B61" s="88"/>
+      <c r="A61" s="101"/>
+      <c r="B61" s="105"/>
       <c r="C61" s="12" t="s">
         <v>202</v>
       </c>
@@ -3810,8 +3817,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="93"/>
-      <c r="B62" s="88"/>
+      <c r="A62" s="101"/>
+      <c r="B62" s="105"/>
       <c r="C62" s="12" t="s">
         <v>251</v>
       </c>
@@ -3824,8 +3831,8 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="93"/>
-      <c r="B63" s="88"/>
+      <c r="A63" s="101"/>
+      <c r="B63" s="105"/>
       <c r="C63" s="12" t="s">
         <v>216</v>
       </c>
@@ -3838,8 +3845,8 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="93"/>
-      <c r="B64" s="88"/>
+      <c r="A64" s="101"/>
+      <c r="B64" s="105"/>
       <c r="C64" s="12" t="s">
         <v>241</v>
       </c>
@@ -3852,18 +3859,18 @@
       </c>
     </row>
     <row r="65" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="96"/>
-      <c r="B65" s="99"/>
+      <c r="A65" s="102"/>
+      <c r="B65" s="111"/>
       <c r="C65" s="42"/>
       <c r="D65" s="42"/>
       <c r="E65" s="43"/>
       <c r="F65" s="42"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="91" t="s">
+      <c r="A66" s="99" t="s">
         <v>86</v>
       </c>
-      <c r="B66" s="94" t="s">
+      <c r="B66" s="103" t="s">
         <v>87</v>
       </c>
       <c r="C66" s="27" t="s">
@@ -3878,8 +3885,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="93"/>
-      <c r="B67" s="88"/>
+      <c r="A67" s="101"/>
+      <c r="B67" s="105"/>
       <c r="C67" s="12" t="s">
         <v>200</v>
       </c>
@@ -3892,13 +3899,13 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="93"/>
-      <c r="B68" s="90"/>
+      <c r="A68" s="101"/>
+      <c r="B68" s="106"/>
       <c r="E68" s="32"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="93"/>
-      <c r="B69" s="100" t="s">
+      <c r="A69" s="101"/>
+      <c r="B69" s="94" t="s">
         <v>305</v>
       </c>
       <c r="C69" s="62" t="s">
@@ -3913,8 +3920,8 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="93"/>
-      <c r="B70" s="101"/>
+      <c r="A70" s="101"/>
+      <c r="B70" s="95"/>
       <c r="C70" s="64" t="s">
         <v>200</v>
       </c>
@@ -3927,16 +3934,16 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="93"/>
-      <c r="B71" s="102"/>
+      <c r="A71" s="101"/>
+      <c r="B71" s="96"/>
       <c r="C71" s="64"/>
       <c r="D71" s="64"/>
       <c r="E71" s="65"/>
       <c r="F71" s="64"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="93"/>
-      <c r="B72" s="98" t="s">
+      <c r="A72" s="101"/>
+      <c r="B72" s="91" t="s">
         <v>6</v>
       </c>
       <c r="C72" s="36" t="s">
@@ -3951,8 +3958,8 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="93"/>
-      <c r="B73" s="95"/>
+      <c r="A73" s="101"/>
+      <c r="B73" s="97"/>
       <c r="C73" s="12" t="s">
         <v>136</v>
       </c>
@@ -3965,8 +3972,8 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="93"/>
-      <c r="B74" s="95"/>
+      <c r="A74" s="101"/>
+      <c r="B74" s="97"/>
       <c r="C74" s="12" t="s">
         <v>152</v>
       </c>
@@ -3979,8 +3986,8 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="93"/>
-      <c r="B75" s="95"/>
+      <c r="A75" s="101"/>
+      <c r="B75" s="97"/>
       <c r="C75" s="12" t="s">
         <v>184</v>
       </c>
@@ -3993,8 +4000,8 @@
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="93"/>
-      <c r="B76" s="95"/>
+      <c r="A76" s="101"/>
+      <c r="B76" s="97"/>
       <c r="C76" s="12" t="s">
         <v>202</v>
       </c>
@@ -4007,8 +4014,8 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="93"/>
-      <c r="B77" s="95"/>
+      <c r="A77" s="101"/>
+      <c r="B77" s="97"/>
       <c r="C77" s="12" t="s">
         <v>210</v>
       </c>
@@ -4021,8 +4028,8 @@
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="93"/>
-      <c r="B78" s="95"/>
+      <c r="A78" s="101"/>
+      <c r="B78" s="97"/>
       <c r="C78" s="12" t="s">
         <v>251</v>
       </c>
@@ -4035,8 +4042,8 @@
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="93"/>
-      <c r="B79" s="95"/>
+      <c r="A79" s="101"/>
+      <c r="B79" s="97"/>
       <c r="C79" s="12" t="s">
         <v>216</v>
       </c>
@@ -4049,8 +4056,8 @@
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="93"/>
-      <c r="B80" s="95"/>
+      <c r="A80" s="101"/>
+      <c r="B80" s="97"/>
       <c r="C80" s="12" t="s">
         <v>241</v>
       </c>
@@ -4063,12 +4070,12 @@
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="93"/>
-      <c r="B81" s="103"/>
+      <c r="A81" s="101"/>
+      <c r="B81" s="93"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="93"/>
-      <c r="B82" s="98" t="s">
+      <c r="A82" s="101"/>
+      <c r="B82" s="91" t="s">
         <v>7</v>
       </c>
       <c r="C82" s="36" t="s">
@@ -4083,8 +4090,8 @@
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="93"/>
-      <c r="B83" s="95"/>
+      <c r="A83" s="101"/>
+      <c r="B83" s="97"/>
       <c r="C83" s="12" t="s">
         <v>137</v>
       </c>
@@ -4097,8 +4104,8 @@
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="93"/>
-      <c r="B84" s="95"/>
+      <c r="A84" s="101"/>
+      <c r="B84" s="97"/>
       <c r="C84" s="12" t="s">
         <v>150</v>
       </c>
@@ -4111,8 +4118,8 @@
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="93"/>
-      <c r="B85" s="95"/>
+      <c r="A85" s="101"/>
+      <c r="B85" s="97"/>
       <c r="C85" s="12" t="s">
         <v>184</v>
       </c>
@@ -4125,8 +4132,8 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="93"/>
-      <c r="B86" s="95"/>
+      <c r="A86" s="101"/>
+      <c r="B86" s="97"/>
       <c r="C86" s="12" t="s">
         <v>202</v>
       </c>
@@ -4139,8 +4146,8 @@
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="93"/>
-      <c r="B87" s="95"/>
+      <c r="A87" s="101"/>
+      <c r="B87" s="97"/>
       <c r="C87" s="12" t="s">
         <v>210</v>
       </c>
@@ -4153,8 +4160,8 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="93"/>
-      <c r="B88" s="95"/>
+      <c r="A88" s="101"/>
+      <c r="B88" s="97"/>
       <c r="C88" s="12" t="s">
         <v>251</v>
       </c>
@@ -4167,8 +4174,8 @@
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="93"/>
-      <c r="B89" s="95"/>
+      <c r="A89" s="101"/>
+      <c r="B89" s="97"/>
       <c r="C89" s="12" t="s">
         <v>216</v>
       </c>
@@ -4181,8 +4188,8 @@
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="93"/>
-      <c r="B90" s="95"/>
+      <c r="A90" s="101"/>
+      <c r="B90" s="97"/>
       <c r="C90" s="12" t="s">
         <v>241</v>
       </c>
@@ -4195,14 +4202,14 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="96"/>
-      <c r="B91" s="104"/>
+      <c r="A91" s="102"/>
+      <c r="B91" s="98"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="91" t="s">
+      <c r="A92" s="99" t="s">
         <v>90</v>
       </c>
-      <c r="B92" s="94" t="s">
+      <c r="B92" s="103" t="s">
         <v>87</v>
       </c>
       <c r="C92" s="27" t="s">
@@ -4217,8 +4224,8 @@
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="92"/>
-      <c r="B93" s="89"/>
+      <c r="A93" s="100"/>
+      <c r="B93" s="104"/>
       <c r="C93" s="54" t="s">
         <v>293</v>
       </c>
@@ -4231,8 +4238,8 @@
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="93"/>
-      <c r="B94" s="88"/>
+      <c r="A94" s="101"/>
+      <c r="B94" s="105"/>
       <c r="C94" s="12" t="s">
         <v>196</v>
       </c>
@@ -4245,13 +4252,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="93"/>
-      <c r="B95" s="90"/>
+      <c r="A95" s="101"/>
+      <c r="B95" s="106"/>
       <c r="E95" s="34"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="93"/>
-      <c r="B96" s="87" t="s">
+      <c r="A96" s="101"/>
+      <c r="B96" s="107" t="s">
         <v>93</v>
       </c>
       <c r="C96" s="36" t="s">
@@ -4266,8 +4273,8 @@
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="93"/>
-      <c r="B97" s="88"/>
+      <c r="A97" s="101"/>
+      <c r="B97" s="105"/>
       <c r="C97" s="12" t="s">
         <v>197</v>
       </c>
@@ -4280,16 +4287,16 @@
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="93"/>
-      <c r="B98" s="90"/>
+      <c r="A98" s="101"/>
+      <c r="B98" s="106"/>
       <c r="C98" s="38"/>
       <c r="D98" s="38"/>
       <c r="E98" s="39"/>
       <c r="F98" s="38"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="93"/>
-      <c r="B99" s="87" t="s">
+      <c r="A99" s="101"/>
+      <c r="B99" s="107" t="s">
         <v>94</v>
       </c>
       <c r="C99" s="12" t="s">
@@ -4304,8 +4311,8 @@
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="93"/>
-      <c r="B100" s="88"/>
+      <c r="A100" s="101"/>
+      <c r="B100" s="105"/>
       <c r="C100" s="12" t="s">
         <v>198</v>
       </c>
@@ -4318,18 +4325,18 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="96"/>
-      <c r="B101" s="99"/>
+      <c r="A101" s="102"/>
+      <c r="B101" s="111"/>
       <c r="C101" s="42"/>
       <c r="D101" s="42"/>
       <c r="E101" s="43"/>
       <c r="F101" s="42"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="91" t="s">
+      <c r="A102" s="99" t="s">
         <v>212</v>
       </c>
-      <c r="B102" s="94" t="s">
+      <c r="B102" s="103" t="s">
         <v>15</v>
       </c>
       <c r="C102" s="27" t="s">
@@ -4344,8 +4351,8 @@
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="92"/>
-      <c r="B103" s="88"/>
+      <c r="A103" s="100"/>
+      <c r="B103" s="105"/>
       <c r="C103" s="12" t="s">
         <v>225</v>
       </c>
@@ -4357,16 +4364,16 @@
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="92"/>
-      <c r="B104" s="90"/>
+      <c r="A104" s="100"/>
+      <c r="B104" s="106"/>
       <c r="C104" s="38"/>
       <c r="D104" s="38"/>
       <c r="E104" s="38"/>
       <c r="F104" s="38"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="92"/>
-      <c r="B105" s="87" t="s">
+      <c r="A105" s="100"/>
+      <c r="B105" s="107" t="s">
         <v>235</v>
       </c>
       <c r="C105" s="12" t="s">
@@ -4380,8 +4387,8 @@
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="92"/>
-      <c r="B106" s="88"/>
+      <c r="A106" s="100"/>
+      <c r="B106" s="105"/>
       <c r="C106" s="12" t="s">
         <v>233</v>
       </c>
@@ -4393,8 +4400,8 @@
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="92"/>
-      <c r="B107" s="88"/>
+      <c r="A107" s="100"/>
+      <c r="B107" s="105"/>
       <c r="C107" s="12" t="s">
         <v>229</v>
       </c>
@@ -4406,8 +4413,8 @@
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="92"/>
-      <c r="B108" s="88"/>
+      <c r="A108" s="100"/>
+      <c r="B108" s="105"/>
       <c r="C108" s="12" t="s">
         <v>231</v>
       </c>
@@ -4419,8 +4426,8 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="92"/>
-      <c r="B109" s="88"/>
+      <c r="A109" s="100"/>
+      <c r="B109" s="105"/>
       <c r="C109" s="12" t="s">
         <v>234</v>
       </c>
@@ -4432,8 +4439,8 @@
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="92"/>
-      <c r="B110" s="88"/>
+      <c r="A110" s="100"/>
+      <c r="B110" s="105"/>
       <c r="C110" s="12" t="s">
         <v>244</v>
       </c>
@@ -4445,8 +4452,8 @@
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="92"/>
-      <c r="B111" s="87" t="s">
+      <c r="A111" s="100"/>
+      <c r="B111" s="107" t="s">
         <v>265</v>
       </c>
       <c r="C111" s="36" t="s">
@@ -4461,8 +4468,8 @@
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="92"/>
-      <c r="B112" s="89"/>
+      <c r="A112" s="100"/>
+      <c r="B112" s="104"/>
       <c r="C112" s="54" t="s">
         <v>261</v>
       </c>
@@ -4475,8 +4482,8 @@
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="92"/>
-      <c r="B113" s="89"/>
+      <c r="A113" s="100"/>
+      <c r="B113" s="104"/>
       <c r="C113" s="54" t="s">
         <v>276</v>
       </c>
@@ -4489,8 +4496,8 @@
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="92"/>
-      <c r="B114" s="89"/>
+      <c r="A114" s="100"/>
+      <c r="B114" s="104"/>
       <c r="C114" s="54" t="s">
         <v>262</v>
       </c>
@@ -4503,8 +4510,8 @@
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="92"/>
-      <c r="B115" s="89"/>
+      <c r="A115" s="100"/>
+      <c r="B115" s="104"/>
       <c r="C115" s="54" t="s">
         <v>278</v>
       </c>
@@ -4517,8 +4524,8 @@
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="92"/>
-      <c r="B116" s="89"/>
+      <c r="A116" s="100"/>
+      <c r="B116" s="104"/>
       <c r="C116" s="54" t="s">
         <v>282</v>
       </c>
@@ -4531,85 +4538,85 @@
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="92"/>
-      <c r="B117" s="89"/>
-      <c r="C117" s="54" t="s">
+      <c r="A117" s="100"/>
+      <c r="B117" s="104"/>
+      <c r="C117" s="112" t="s">
+        <v>332</v>
+      </c>
+      <c r="D117" s="112" t="s">
+        <v>331</v>
+      </c>
+      <c r="E117" s="112"/>
+      <c r="F117" s="112" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" s="100"/>
+      <c r="B118" s="104"/>
+      <c r="C118" s="54" t="s">
         <v>259</v>
       </c>
-      <c r="D117" s="12" t="s">
+      <c r="D118" s="12" t="s">
         <v>281</v>
       </c>
-      <c r="E117" s="54"/>
-      <c r="F117" s="54" t="s">
+      <c r="E118" s="54"/>
+      <c r="F118" s="54" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="92"/>
-      <c r="B118" s="89"/>
-      <c r="C118" s="54" t="s">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119" s="100"/>
+      <c r="B119" s="104"/>
+      <c r="C119" s="54" t="s">
         <v>263</v>
       </c>
-      <c r="D118" s="54" t="s">
+      <c r="D119" s="54" t="s">
         <v>272</v>
       </c>
-      <c r="E118" s="54"/>
-      <c r="F118" s="12" t="s">
+      <c r="E119" s="54"/>
+      <c r="F119" s="12" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="92"/>
-      <c r="B119" s="89"/>
-      <c r="C119" s="54" t="s">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120" s="100"/>
+      <c r="B120" s="104"/>
+      <c r="C120" s="54" t="s">
         <v>264</v>
       </c>
-      <c r="D119" s="54" t="s">
+      <c r="D120" s="54" t="s">
         <v>273</v>
       </c>
-      <c r="E119" s="54"/>
-      <c r="F119" s="54" t="s">
+      <c r="E120" s="54"/>
+      <c r="F120" s="54" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="92"/>
-      <c r="B120" s="87" t="s">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" s="100"/>
+      <c r="B121" s="107" t="s">
         <v>283</v>
       </c>
-      <c r="C120" s="36" t="s">
+      <c r="C121" s="36" t="s">
         <v>285</v>
       </c>
-      <c r="D120" s="36" t="s">
+      <c r="D121" s="36" t="s">
         <v>284</v>
       </c>
-      <c r="E120" s="36"/>
-      <c r="F120" s="36" t="s">
+      <c r="E121" s="36"/>
+      <c r="F121" s="36" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="92"/>
-      <c r="B121" s="89"/>
-      <c r="C121" s="54" t="s">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" s="100"/>
+      <c r="B122" s="104"/>
+      <c r="C122" s="54" t="s">
         <v>286</v>
       </c>
-      <c r="D121" s="54" t="s">
+      <c r="D122" s="54" t="s">
         <v>287</v>
-      </c>
-      <c r="E121" s="54"/>
-      <c r="F121" s="54" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="92"/>
-      <c r="B122" s="89"/>
-      <c r="C122" s="54" t="s">
-        <v>288</v>
-      </c>
-      <c r="D122" s="54" t="s">
-        <v>290</v>
       </c>
       <c r="E122" s="54"/>
       <c r="F122" s="54" t="s">
@@ -4617,66 +4624,73 @@
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="92"/>
-      <c r="B123" s="89"/>
-      <c r="C123" s="12" t="s">
+      <c r="A123" s="100"/>
+      <c r="B123" s="104"/>
+      <c r="C123" s="54" t="s">
+        <v>288</v>
+      </c>
+      <c r="D123" s="54" t="s">
+        <v>290</v>
+      </c>
+      <c r="E123" s="54"/>
+      <c r="F123" s="54" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" s="100"/>
+      <c r="B124" s="104"/>
+      <c r="C124" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="D123" s="12" t="s">
+      <c r="D124" s="12" t="s">
         <v>291</v>
       </c>
-      <c r="F123" s="12" t="s">
+      <c r="F124" s="12" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="92"/>
-      <c r="B124" s="90"/>
-    </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="92"/>
-      <c r="B125" s="87" t="s">
+      <c r="A125" s="100"/>
+      <c r="B125" s="106"/>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126" s="100"/>
+      <c r="B126" s="107" t="s">
         <v>294</v>
       </c>
-      <c r="C125" s="36" t="s">
+      <c r="C126" s="36" t="s">
         <v>295</v>
       </c>
-      <c r="D125" s="36" t="s">
+      <c r="D126" s="36" t="s">
         <v>296</v>
       </c>
-      <c r="E125" s="36"/>
-      <c r="F125" s="36" t="s">
+      <c r="E126" s="36"/>
+      <c r="F126" s="36" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="92"/>
-      <c r="B126" s="88"/>
-      <c r="C126" s="12" t="s">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127" s="100"/>
+      <c r="B127" s="105"/>
+      <c r="C127" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="D126" s="12" t="s">
+      <c r="D127" s="12" t="s">
         <v>298</v>
       </c>
-      <c r="F126" s="12" t="s">
+      <c r="F127" s="12" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="92"/>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="B23:B32"/>
-    <mergeCell ref="B69:B71"/>
-    <mergeCell ref="B72:B81"/>
-    <mergeCell ref="B82:B91"/>
-    <mergeCell ref="A92:A101"/>
-    <mergeCell ref="B92:B95"/>
-    <mergeCell ref="B96:B98"/>
-    <mergeCell ref="B125:B126"/>
-    <mergeCell ref="B120:B124"/>
-    <mergeCell ref="A102:A127"/>
+    <mergeCell ref="B126:B127"/>
+    <mergeCell ref="B121:B125"/>
+    <mergeCell ref="A102:A128"/>
     <mergeCell ref="A2:A43"/>
     <mergeCell ref="B2:B11"/>
     <mergeCell ref="B12:B22"/>
@@ -4687,9 +4701,16 @@
     <mergeCell ref="B99:B101"/>
     <mergeCell ref="B66:B68"/>
     <mergeCell ref="B105:B110"/>
-    <mergeCell ref="B111:B119"/>
+    <mergeCell ref="B111:B120"/>
     <mergeCell ref="B102:B104"/>
     <mergeCell ref="A66:A91"/>
+    <mergeCell ref="B23:B32"/>
+    <mergeCell ref="B69:B71"/>
+    <mergeCell ref="B72:B81"/>
+    <mergeCell ref="B82:B91"/>
+    <mergeCell ref="A92:A101"/>
+    <mergeCell ref="B92:B95"/>
+    <mergeCell ref="B96:B98"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Ammoniak/Ammoniak_Brownfield_H2_N2_HB_Pipeline_Höchst/Datenbank.xlsx
+++ b/Ammoniak/Ammoniak_Brownfield_H2_N2_HB_Pipeline_Höchst/Datenbank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Ammoniak\Ammoniak_Brownfield_H2_N2_HB_Pipeline_Höchst\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1E50EA-742C-45CD-B53B-99C9E4742025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44889D5C-3BEF-4D7E-B60E-71222B72D899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -1340,7 +1340,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1425,6 +1425,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1477,7 +1478,49 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1494,52 +1537,12 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1898,10 +1901,10 @@
       <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="75" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="85" t="s">
+      <c r="B2" s="86" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1918,8 +1921,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="75"/>
-      <c r="B3" s="86"/>
+      <c r="A3" s="76"/>
+      <c r="B3" s="87"/>
       <c r="C3" t="s">
         <v>102</v>
       </c>
@@ -1934,8 +1937,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="75"/>
-      <c r="B4" s="86"/>
+      <c r="A4" s="76"/>
+      <c r="B4" s="87"/>
       <c r="C4" t="s">
         <v>12</v>
       </c>
@@ -1950,8 +1953,8 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="75"/>
-      <c r="B5" s="86"/>
+      <c r="A5" s="76"/>
+      <c r="B5" s="87"/>
       <c r="C5" t="s">
         <v>13</v>
       </c>
@@ -1966,8 +1969,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="75"/>
-      <c r="B6" s="86"/>
+      <c r="A6" s="76"/>
+      <c r="B6" s="87"/>
       <c r="C6" t="s">
         <v>15</v>
       </c>
@@ -1982,8 +1985,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="75"/>
-      <c r="B7" s="86"/>
+      <c r="A7" s="76"/>
+      <c r="B7" s="87"/>
       <c r="C7" t="s">
         <v>17</v>
       </c>
@@ -1998,8 +2001,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="75"/>
-      <c r="B8" s="87" t="s">
+      <c r="A8" s="76"/>
+      <c r="B8" s="88" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -2016,8 +2019,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="75"/>
-      <c r="B9" s="86"/>
+      <c r="A9" s="76"/>
+      <c r="B9" s="87"/>
       <c r="C9" t="s">
         <v>105</v>
       </c>
@@ -2032,8 +2035,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="75"/>
-      <c r="B10" s="86"/>
+      <c r="A10" s="76"/>
+      <c r="B10" s="87"/>
       <c r="C10" t="s">
         <v>12</v>
       </c>
@@ -2048,8 +2051,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="75"/>
-      <c r="B11" s="86"/>
+      <c r="A11" s="76"/>
+      <c r="B11" s="87"/>
       <c r="C11" t="s">
         <v>13</v>
       </c>
@@ -2065,8 +2068,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="75"/>
-      <c r="B12" s="86"/>
+      <c r="A12" s="76"/>
+      <c r="B12" s="87"/>
       <c r="C12" t="s">
         <v>110</v>
       </c>
@@ -2081,8 +2084,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="75"/>
-      <c r="B13" s="86"/>
+      <c r="A13" s="76"/>
+      <c r="B13" s="87"/>
       <c r="C13" t="s">
         <v>109</v>
       </c>
@@ -2097,8 +2100,8 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="75"/>
-      <c r="B14" s="86"/>
+      <c r="A14" s="76"/>
+      <c r="B14" s="87"/>
       <c r="C14" t="s">
         <v>15</v>
       </c>
@@ -2113,8 +2116,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="75"/>
-      <c r="B15" s="88"/>
+      <c r="A15" s="76"/>
+      <c r="B15" s="89"/>
       <c r="C15" s="5" t="s">
         <v>17</v>
       </c>
@@ -2129,8 +2132,8 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="75"/>
-      <c r="B16" s="80" t="s">
+      <c r="A16" s="76"/>
+      <c r="B16" s="81" t="s">
         <v>4</v>
       </c>
       <c r="C16" s="4" t="s">
@@ -2148,8 +2151,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="75"/>
-      <c r="B17" s="90"/>
+      <c r="A17" s="76"/>
+      <c r="B17" s="91"/>
       <c r="C17" s="50" t="s">
         <v>12</v>
       </c>
@@ -2164,8 +2167,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="75"/>
-      <c r="B18" s="90"/>
+      <c r="A18" s="76"/>
+      <c r="B18" s="91"/>
       <c r="C18" s="50" t="s">
         <v>13</v>
       </c>
@@ -2180,8 +2183,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="75"/>
-      <c r="B19" s="90"/>
+      <c r="A19" s="76"/>
+      <c r="B19" s="91"/>
       <c r="C19" s="50" t="s">
         <v>15</v>
       </c>
@@ -2196,8 +2199,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="75"/>
-      <c r="B20" s="81"/>
+      <c r="A20" s="76"/>
+      <c r="B20" s="82"/>
       <c r="C20" s="5" t="s">
         <v>17</v>
       </c>
@@ -2212,8 +2215,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="75"/>
-      <c r="B21" s="89" t="s">
+      <c r="A21" s="76"/>
+      <c r="B21" s="90" t="s">
         <v>310</v>
       </c>
       <c r="C21" t="s">
@@ -2222,7 +2225,7 @@
       <c r="D21" t="s">
         <v>311</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="113">
         <v>4</v>
       </c>
       <c r="F21" t="s">
@@ -2230,15 +2233,15 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="75"/>
-      <c r="B22" s="89"/>
+      <c r="A22" s="76"/>
+      <c r="B22" s="90"/>
       <c r="C22" t="s">
         <v>12</v>
       </c>
       <c r="D22" t="s">
         <v>312</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="113">
         <v>3800</v>
       </c>
       <c r="F22" t="s">
@@ -2246,15 +2249,15 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="75"/>
-      <c r="B23" s="89"/>
+      <c r="A23" s="76"/>
+      <c r="B23" s="90"/>
       <c r="C23" t="s">
         <v>13</v>
       </c>
       <c r="D23" t="s">
         <v>313</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="114">
         <v>0.06</v>
       </c>
       <c r="F23" t="s">
@@ -2262,15 +2265,15 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="75"/>
-      <c r="B24" s="89"/>
+      <c r="A24" s="76"/>
+      <c r="B24" s="90"/>
       <c r="C24" t="s">
         <v>329</v>
       </c>
       <c r="D24" t="s">
         <v>330</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="114">
         <v>0.95</v>
       </c>
       <c r="F24" t="s">
@@ -2278,15 +2281,15 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="75"/>
-      <c r="B25" s="89"/>
+      <c r="A25" s="76"/>
+      <c r="B25" s="90"/>
       <c r="C25" t="s">
         <v>15</v>
       </c>
       <c r="D25" t="s">
         <v>314</v>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="115">
         <v>15</v>
       </c>
       <c r="F25" t="s">
@@ -2294,15 +2297,15 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="75"/>
-      <c r="B26" s="89"/>
+      <c r="A26" s="76"/>
+      <c r="B26" s="90"/>
       <c r="C26" t="s">
         <v>17</v>
       </c>
       <c r="D26" t="s">
         <v>315</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="114">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="F26" t="s">
@@ -2310,10 +2313,10 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="74" t="s">
+      <c r="A27" s="75" t="s">
         <v>85</v>
       </c>
-      <c r="B27" s="78" t="s">
+      <c r="B27" s="79" t="s">
         <v>5</v>
       </c>
       <c r="C27" s="2" t="s">
@@ -2330,8 +2333,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="75"/>
-      <c r="B28" s="79"/>
+      <c r="A28" s="76"/>
+      <c r="B28" s="80"/>
       <c r="C28" t="s">
         <v>13</v>
       </c>
@@ -2346,8 +2349,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="75"/>
-      <c r="B29" s="79"/>
+      <c r="A29" s="76"/>
+      <c r="B29" s="80"/>
       <c r="C29" t="s">
         <v>15</v>
       </c>
@@ -2362,8 +2365,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="75"/>
-      <c r="B30" s="79"/>
+      <c r="A30" s="76"/>
+      <c r="B30" s="80"/>
       <c r="C30" t="s">
         <v>22</v>
       </c>
@@ -2378,8 +2381,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="75"/>
-      <c r="B31" s="79"/>
+      <c r="A31" s="76"/>
+      <c r="B31" s="80"/>
       <c r="C31" t="s">
         <v>47</v>
       </c>
@@ -2394,8 +2397,8 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="75"/>
-      <c r="B32" s="79"/>
+      <c r="A32" s="76"/>
+      <c r="B32" s="80"/>
       <c r="C32" t="s">
         <v>48</v>
       </c>
@@ -2410,8 +2413,8 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="75"/>
-      <c r="B33" s="79"/>
+      <c r="A33" s="76"/>
+      <c r="B33" s="80"/>
       <c r="C33" t="s">
         <v>17</v>
       </c>
@@ -2426,8 +2429,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="75"/>
-      <c r="B34" s="79"/>
+      <c r="A34" s="76"/>
+      <c r="B34" s="80"/>
       <c r="C34" t="s">
         <v>114</v>
       </c>
@@ -2442,8 +2445,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="75"/>
-      <c r="B35" s="80" t="s">
+      <c r="A35" s="76"/>
+      <c r="B35" s="81" t="s">
         <v>258</v>
       </c>
       <c r="C35" s="4" t="s">
@@ -2460,8 +2463,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="75"/>
-      <c r="B36" s="83"/>
+      <c r="A36" s="76"/>
+      <c r="B36" s="84"/>
       <c r="C36" s="50" t="s">
         <v>23</v>
       </c>
@@ -2477,8 +2480,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="75"/>
-      <c r="B37" s="83"/>
+      <c r="A37" s="76"/>
+      <c r="B37" s="84"/>
       <c r="C37" s="50" t="s">
         <v>18</v>
       </c>
@@ -2493,8 +2496,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="75"/>
-      <c r="B38" s="83"/>
+      <c r="A38" s="76"/>
+      <c r="B38" s="84"/>
       <c r="C38" s="50" t="s">
         <v>19</v>
       </c>
@@ -2509,8 +2512,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="75"/>
-      <c r="B39" s="83"/>
+      <c r="A39" s="76"/>
+      <c r="B39" s="84"/>
       <c r="C39" s="50" t="s">
         <v>47</v>
       </c>
@@ -2525,8 +2528,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="75"/>
-      <c r="B40" s="83"/>
+      <c r="A40" s="76"/>
+      <c r="B40" s="84"/>
       <c r="C40" s="50" t="s">
         <v>48</v>
       </c>
@@ -2541,8 +2544,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="75"/>
-      <c r="B41" s="83"/>
+      <c r="A41" s="76"/>
+      <c r="B41" s="84"/>
       <c r="C41" s="50" t="s">
         <v>115</v>
       </c>
@@ -2557,8 +2560,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="75"/>
-      <c r="B42" s="83"/>
+      <c r="A42" s="76"/>
+      <c r="B42" s="84"/>
       <c r="C42" s="50" t="s">
         <v>114</v>
       </c>
@@ -2573,8 +2576,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="75"/>
-      <c r="B43" s="83"/>
+      <c r="A43" s="76"/>
+      <c r="B43" s="84"/>
       <c r="C43" s="50" t="s">
         <v>15</v>
       </c>
@@ -2589,8 +2592,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="76"/>
-      <c r="B44" s="84"/>
+      <c r="A44" s="77"/>
+      <c r="B44" s="85"/>
       <c r="C44" s="14" t="s">
         <v>17</v>
       </c>
@@ -2605,7 +2608,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="74" t="s">
+      <c r="A45" s="75" t="s">
         <v>86</v>
       </c>
       <c r="B45" s="56" t="s">
@@ -2625,7 +2628,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="77"/>
+      <c r="A46" s="78"/>
       <c r="B46" s="66" t="s">
         <v>302</v>
       </c>
@@ -2643,7 +2646,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="77"/>
+      <c r="A47" s="78"/>
       <c r="B47" s="59" t="s">
         <v>299</v>
       </c>
@@ -2661,8 +2664,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="75"/>
-      <c r="B48" s="80" t="s">
+      <c r="A48" s="76"/>
+      <c r="B48" s="81" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="4" t="s">
@@ -2679,8 +2682,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="75"/>
-      <c r="B49" s="79"/>
+      <c r="A49" s="76"/>
+      <c r="B49" s="80"/>
       <c r="C49" t="s">
         <v>12</v>
       </c>
@@ -2695,8 +2698,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="75"/>
-      <c r="B50" s="79"/>
+      <c r="A50" s="76"/>
+      <c r="B50" s="80"/>
       <c r="C50" t="s">
         <v>19</v>
       </c>
@@ -2711,8 +2714,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="75"/>
-      <c r="B51" s="79"/>
+      <c r="A51" s="76"/>
+      <c r="B51" s="80"/>
       <c r="C51" t="s">
         <v>20</v>
       </c>
@@ -2727,8 +2730,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="75"/>
-      <c r="B52" s="79"/>
+      <c r="A52" s="76"/>
+      <c r="B52" s="80"/>
       <c r="C52" t="s">
         <v>15</v>
       </c>
@@ -2743,8 +2746,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="75"/>
-      <c r="B53" s="79"/>
+      <c r="A53" s="76"/>
+      <c r="B53" s="80"/>
       <c r="C53" t="s">
         <v>82</v>
       </c>
@@ -2759,8 +2762,8 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="75"/>
-      <c r="B54" s="81"/>
+      <c r="A54" s="76"/>
+      <c r="B54" s="82"/>
       <c r="C54" s="5" t="s">
         <v>17</v>
       </c>
@@ -2775,8 +2778,8 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="75"/>
-      <c r="B55" s="80" t="s">
+      <c r="A55" s="76"/>
+      <c r="B55" s="81" t="s">
         <v>7</v>
       </c>
       <c r="C55" s="4" t="s">
@@ -2793,8 +2796,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="75"/>
-      <c r="B56" s="79"/>
+      <c r="A56" s="76"/>
+      <c r="B56" s="80"/>
       <c r="C56" t="s">
         <v>12</v>
       </c>
@@ -2809,8 +2812,8 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="75"/>
-      <c r="B57" s="79"/>
+      <c r="A57" s="76"/>
+      <c r="B57" s="80"/>
       <c r="C57" t="s">
         <v>19</v>
       </c>
@@ -2825,8 +2828,8 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="75"/>
-      <c r="B58" s="79"/>
+      <c r="A58" s="76"/>
+      <c r="B58" s="80"/>
       <c r="C58" t="s">
         <v>20</v>
       </c>
@@ -2841,8 +2844,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="75"/>
-      <c r="B59" s="79"/>
+      <c r="A59" s="76"/>
+      <c r="B59" s="80"/>
       <c r="C59" t="s">
         <v>15</v>
       </c>
@@ -2857,8 +2860,8 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="75"/>
-      <c r="B60" s="79"/>
+      <c r="A60" s="76"/>
+      <c r="B60" s="80"/>
       <c r="C60" t="s">
         <v>82</v>
       </c>
@@ -2873,8 +2876,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="76"/>
-      <c r="B61" s="82"/>
+      <c r="A61" s="77"/>
+      <c r="B61" s="83"/>
       <c r="C61" s="14" t="s">
         <v>17</v>
       </c>
@@ -2889,7 +2892,7 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="74" t="s">
+      <c r="A62" s="75" t="s">
         <v>90</v>
       </c>
       <c r="B62" s="16" t="s">
@@ -2909,7 +2912,7 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="75"/>
+      <c r="A63" s="76"/>
       <c r="B63" s="17" t="s">
         <v>93</v>
       </c>
@@ -2927,7 +2930,7 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="76"/>
+      <c r="A64" s="77"/>
       <c r="B64" s="1" t="s">
         <v>94</v>
       </c>
@@ -3000,10 +3003,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="99" t="s">
+      <c r="A2" s="96" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="103" t="s">
+      <c r="B2" s="99" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="27" t="s">
@@ -3018,8 +3021,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="101"/>
-      <c r="B3" s="105"/>
+      <c r="A3" s="98"/>
+      <c r="B3" s="93"/>
       <c r="C3" s="12" t="s">
         <v>136</v>
       </c>
@@ -3032,8 +3035,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="101"/>
-      <c r="B4" s="105"/>
+      <c r="A4" s="98"/>
+      <c r="B4" s="93"/>
       <c r="C4" s="12" t="s">
         <v>102</v>
       </c>
@@ -3046,8 +3049,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="101"/>
-      <c r="B5" s="105"/>
+      <c r="A5" s="98"/>
+      <c r="B5" s="93"/>
       <c r="C5" s="12" t="s">
         <v>172</v>
       </c>
@@ -3060,8 +3063,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="101"/>
-      <c r="B6" s="105"/>
+      <c r="A6" s="98"/>
+      <c r="B6" s="93"/>
       <c r="C6" s="12" t="s">
         <v>184</v>
       </c>
@@ -3074,8 +3077,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="101"/>
-      <c r="B7" s="105"/>
+      <c r="A7" s="98"/>
+      <c r="B7" s="93"/>
       <c r="C7" s="12" t="s">
         <v>202</v>
       </c>
@@ -3088,8 +3091,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="101"/>
-      <c r="B8" s="105"/>
+      <c r="A8" s="98"/>
+      <c r="B8" s="93"/>
       <c r="C8" s="12" t="s">
         <v>251</v>
       </c>
@@ -3102,8 +3105,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="101"/>
-      <c r="B9" s="105"/>
+      <c r="A9" s="98"/>
+      <c r="B9" s="93"/>
       <c r="C9" s="12" t="s">
         <v>216</v>
       </c>
@@ -3116,8 +3119,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="101"/>
-      <c r="B10" s="105"/>
+      <c r="A10" s="98"/>
+      <c r="B10" s="93"/>
       <c r="C10" s="12" t="s">
         <v>241</v>
       </c>
@@ -3130,13 +3133,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="101"/>
-      <c r="B11" s="105"/>
+      <c r="A11" s="98"/>
+      <c r="B11" s="93"/>
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="101"/>
-      <c r="B12" s="107" t="s">
+      <c r="A12" s="98"/>
+      <c r="B12" s="92" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="36" t="s">
@@ -3151,8 +3154,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="101"/>
-      <c r="B13" s="105"/>
+      <c r="A13" s="98"/>
+      <c r="B13" s="93"/>
       <c r="C13" s="12" t="s">
         <v>177</v>
       </c>
@@ -3165,8 +3168,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="101"/>
-      <c r="B14" s="105"/>
+      <c r="A14" s="98"/>
+      <c r="B14" s="93"/>
       <c r="C14" s="12" t="s">
         <v>180</v>
       </c>
@@ -3179,8 +3182,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="101"/>
-      <c r="B15" s="105"/>
+      <c r="A15" s="98"/>
+      <c r="B15" s="93"/>
       <c r="C15" s="12" t="s">
         <v>181</v>
       </c>
@@ -3193,8 +3196,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="101"/>
-      <c r="B16" s="105"/>
+      <c r="A16" s="98"/>
+      <c r="B16" s="93"/>
       <c r="C16" s="12" t="s">
         <v>102</v>
       </c>
@@ -3207,8 +3210,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="101"/>
-      <c r="B17" s="105"/>
+      <c r="A17" s="98"/>
+      <c r="B17" s="93"/>
       <c r="C17" s="12" t="s">
         <v>184</v>
       </c>
@@ -3221,8 +3224,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="101"/>
-      <c r="B18" s="105"/>
+      <c r="A18" s="98"/>
+      <c r="B18" s="93"/>
       <c r="C18" s="12" t="s">
         <v>202</v>
       </c>
@@ -3235,8 +3238,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="101"/>
-      <c r="B19" s="105"/>
+      <c r="A19" s="98"/>
+      <c r="B19" s="93"/>
       <c r="C19" s="12" t="s">
         <v>251</v>
       </c>
@@ -3249,8 +3252,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="101"/>
-      <c r="B20" s="105"/>
+      <c r="A20" s="98"/>
+      <c r="B20" s="93"/>
       <c r="C20" s="12" t="s">
         <v>216</v>
       </c>
@@ -3263,8 +3266,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="101"/>
-      <c r="B21" s="105"/>
+      <c r="A21" s="98"/>
+      <c r="B21" s="93"/>
       <c r="C21" s="12" t="s">
         <v>241</v>
       </c>
@@ -3277,16 +3280,16 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="101"/>
-      <c r="B22" s="106"/>
+      <c r="A22" s="98"/>
+      <c r="B22" s="95"/>
       <c r="C22" s="38"/>
       <c r="D22" s="38"/>
       <c r="E22" s="39"/>
       <c r="F22" s="38"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="101"/>
-      <c r="B23" s="91" t="s">
+      <c r="A23" s="98"/>
+      <c r="B23" s="105" t="s">
         <v>4</v>
       </c>
       <c r="C23" s="36" t="s">
@@ -3301,8 +3304,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="101"/>
-      <c r="B24" s="92"/>
+      <c r="A24" s="98"/>
+      <c r="B24" s="107"/>
       <c r="C24" s="54" t="s">
         <v>136</v>
       </c>
@@ -3315,8 +3318,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="101"/>
-      <c r="B25" s="92"/>
+      <c r="A25" s="98"/>
+      <c r="B25" s="107"/>
       <c r="C25" s="54" t="s">
         <v>102</v>
       </c>
@@ -3329,8 +3332,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="101"/>
-      <c r="B26" s="92"/>
+      <c r="A26" s="98"/>
+      <c r="B26" s="107"/>
       <c r="C26" s="54" t="s">
         <v>174</v>
       </c>
@@ -3343,8 +3346,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="101"/>
-      <c r="B27" s="92"/>
+      <c r="A27" s="98"/>
+      <c r="B27" s="107"/>
       <c r="C27" s="54" t="s">
         <v>184</v>
       </c>
@@ -3357,8 +3360,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="101"/>
-      <c r="B28" s="92"/>
+      <c r="A28" s="98"/>
+      <c r="B28" s="107"/>
       <c r="C28" s="54" t="s">
         <v>202</v>
       </c>
@@ -3371,8 +3374,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="101"/>
-      <c r="B29" s="92"/>
+      <c r="A29" s="98"/>
+      <c r="B29" s="107"/>
       <c r="C29" s="54" t="s">
         <v>251</v>
       </c>
@@ -3385,8 +3388,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="101"/>
-      <c r="B30" s="92"/>
+      <c r="A30" s="98"/>
+      <c r="B30" s="107"/>
       <c r="C30" s="54" t="s">
         <v>216</v>
       </c>
@@ -3399,8 +3402,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="101"/>
-      <c r="B31" s="92"/>
+      <c r="A31" s="98"/>
+      <c r="B31" s="107"/>
       <c r="C31" s="54" t="s">
         <v>241</v>
       </c>
@@ -3413,16 +3416,16 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="101"/>
-      <c r="B32" s="93"/>
+      <c r="A32" s="98"/>
+      <c r="B32" s="108"/>
       <c r="C32" s="38"/>
       <c r="D32" s="38"/>
       <c r="E32" s="39"/>
       <c r="F32" s="38"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="101"/>
-      <c r="B33" s="108" t="s">
+      <c r="A33" s="98"/>
+      <c r="B33" s="100" t="s">
         <v>310</v>
       </c>
       <c r="C33" s="12" t="s">
@@ -3437,8 +3440,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="101"/>
-      <c r="B34" s="89"/>
+      <c r="A34" s="98"/>
+      <c r="B34" s="90"/>
       <c r="C34" s="12" t="s">
         <v>136</v>
       </c>
@@ -3451,8 +3454,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="101"/>
-      <c r="B35" s="89"/>
+      <c r="A35" s="98"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="12" t="s">
         <v>102</v>
       </c>
@@ -3465,8 +3468,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="101"/>
-      <c r="B36" s="89"/>
+      <c r="A36" s="98"/>
+      <c r="B36" s="90"/>
       <c r="C36" s="12" t="s">
         <v>180</v>
       </c>
@@ -3479,8 +3482,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="101"/>
-      <c r="B37" s="89"/>
+      <c r="A37" s="98"/>
+      <c r="B37" s="90"/>
       <c r="C37" s="12" t="s">
         <v>327</v>
       </c>
@@ -3493,8 +3496,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="101"/>
-      <c r="B38" s="89"/>
+      <c r="A38" s="98"/>
+      <c r="B38" s="90"/>
       <c r="C38" s="12" t="s">
         <v>184</v>
       </c>
@@ -3507,8 +3510,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="101"/>
-      <c r="B39" s="89"/>
+      <c r="A39" s="98"/>
+      <c r="B39" s="90"/>
       <c r="C39" s="12" t="s">
         <v>202</v>
       </c>
@@ -3521,8 +3524,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="101"/>
-      <c r="B40" s="89"/>
+      <c r="A40" s="98"/>
+      <c r="B40" s="90"/>
       <c r="C40" s="12" t="s">
         <v>251</v>
       </c>
@@ -3535,8 +3538,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="101"/>
-      <c r="B41" s="89"/>
+      <c r="A41" s="98"/>
+      <c r="B41" s="90"/>
       <c r="C41" s="12" t="s">
         <v>216</v>
       </c>
@@ -3549,8 +3552,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="101"/>
-      <c r="B42" s="89"/>
+      <c r="A42" s="98"/>
+      <c r="B42" s="90"/>
       <c r="C42" s="12" t="s">
         <v>241</v>
       </c>
@@ -3563,15 +3566,15 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="101"/>
-      <c r="B43" s="109"/>
+      <c r="A43" s="98"/>
+      <c r="B43" s="101"/>
       <c r="E43" s="34"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="99" t="s">
+      <c r="A44" s="96" t="s">
         <v>85</v>
       </c>
-      <c r="B44" s="110" t="s">
+      <c r="B44" s="103" t="s">
         <v>5</v>
       </c>
       <c r="C44" s="27" t="s">
@@ -3586,8 +3589,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="101"/>
-      <c r="B45" s="97"/>
+      <c r="A45" s="98"/>
+      <c r="B45" s="104"/>
       <c r="C45" s="12" t="s">
         <v>140</v>
       </c>
@@ -3600,8 +3603,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="101"/>
-      <c r="B46" s="97"/>
+      <c r="A46" s="98"/>
+      <c r="B46" s="104"/>
       <c r="C46" s="12" t="s">
         <v>169</v>
       </c>
@@ -3614,8 +3617,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="101"/>
-      <c r="B47" s="97"/>
+      <c r="A47" s="98"/>
+      <c r="B47" s="104"/>
       <c r="C47" s="12" t="s">
         <v>170</v>
       </c>
@@ -3628,8 +3631,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="101"/>
-      <c r="B48" s="97"/>
+      <c r="A48" s="98"/>
+      <c r="B48" s="104"/>
       <c r="C48" s="12" t="s">
         <v>184</v>
       </c>
@@ -3642,8 +3645,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="101"/>
-      <c r="B49" s="97"/>
+      <c r="A49" s="98"/>
+      <c r="B49" s="104"/>
       <c r="C49" s="12" t="s">
         <v>202</v>
       </c>
@@ -3656,8 +3659,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="101"/>
-      <c r="B50" s="97"/>
+      <c r="A50" s="98"/>
+      <c r="B50" s="104"/>
       <c r="C50" s="12" t="s">
         <v>251</v>
       </c>
@@ -3670,8 +3673,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="101"/>
-      <c r="B51" s="97"/>
+      <c r="A51" s="98"/>
+      <c r="B51" s="104"/>
       <c r="C51" s="12" t="s">
         <v>216</v>
       </c>
@@ -3684,8 +3687,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="101"/>
-      <c r="B52" s="97"/>
+      <c r="A52" s="98"/>
+      <c r="B52" s="104"/>
       <c r="C52" s="12" t="s">
         <v>241</v>
       </c>
@@ -3698,13 +3701,13 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="101"/>
-      <c r="B53" s="97"/>
+      <c r="A53" s="98"/>
+      <c r="B53" s="104"/>
       <c r="E53" s="34"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="101"/>
-      <c r="B54" s="91" t="s">
+      <c r="A54" s="98"/>
+      <c r="B54" s="105" t="s">
         <v>8</v>
       </c>
       <c r="C54" s="36" t="s">
@@ -3719,8 +3722,8 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="101"/>
-      <c r="B55" s="97"/>
+      <c r="A55" s="98"/>
+      <c r="B55" s="104"/>
       <c r="C55" s="12" t="s">
         <v>142</v>
       </c>
@@ -3733,8 +3736,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="101"/>
-      <c r="B56" s="105"/>
+      <c r="A56" s="98"/>
+      <c r="B56" s="93"/>
       <c r="C56" s="12" t="s">
         <v>140</v>
       </c>
@@ -3747,8 +3750,8 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="101"/>
-      <c r="B57" s="105"/>
+      <c r="A57" s="98"/>
+      <c r="B57" s="93"/>
       <c r="C57" s="12" t="s">
         <v>136</v>
       </c>
@@ -3761,8 +3764,8 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="101"/>
-      <c r="B58" s="105"/>
+      <c r="A58" s="98"/>
+      <c r="B58" s="93"/>
       <c r="C58" s="12" t="s">
         <v>157</v>
       </c>
@@ -3775,8 +3778,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="101"/>
-      <c r="B59" s="105"/>
+      <c r="A59" s="98"/>
+      <c r="B59" s="93"/>
       <c r="C59" s="12" t="s">
         <v>158</v>
       </c>
@@ -3789,8 +3792,8 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="101"/>
-      <c r="B60" s="105"/>
+      <c r="A60" s="98"/>
+      <c r="B60" s="93"/>
       <c r="C60" s="12" t="s">
         <v>184</v>
       </c>
@@ -3803,8 +3806,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="101"/>
-      <c r="B61" s="105"/>
+      <c r="A61" s="98"/>
+      <c r="B61" s="93"/>
       <c r="C61" s="12" t="s">
         <v>202</v>
       </c>
@@ -3817,8 +3820,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="101"/>
-      <c r="B62" s="105"/>
+      <c r="A62" s="98"/>
+      <c r="B62" s="93"/>
       <c r="C62" s="12" t="s">
         <v>251</v>
       </c>
@@ -3831,8 +3834,8 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="101"/>
-      <c r="B63" s="105"/>
+      <c r="A63" s="98"/>
+      <c r="B63" s="93"/>
       <c r="C63" s="12" t="s">
         <v>216</v>
       </c>
@@ -3845,8 +3848,8 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="101"/>
-      <c r="B64" s="105"/>
+      <c r="A64" s="98"/>
+      <c r="B64" s="93"/>
       <c r="C64" s="12" t="s">
         <v>241</v>
       </c>
@@ -3860,17 +3863,17 @@
     </row>
     <row r="65" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="102"/>
-      <c r="B65" s="111"/>
+      <c r="B65" s="106"/>
       <c r="C65" s="42"/>
       <c r="D65" s="42"/>
       <c r="E65" s="43"/>
       <c r="F65" s="42"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="99" t="s">
+      <c r="A66" s="96" t="s">
         <v>86</v>
       </c>
-      <c r="B66" s="103" t="s">
+      <c r="B66" s="99" t="s">
         <v>87</v>
       </c>
       <c r="C66" s="27" t="s">
@@ -3885,8 +3888,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="101"/>
-      <c r="B67" s="105"/>
+      <c r="A67" s="98"/>
+      <c r="B67" s="93"/>
       <c r="C67" s="12" t="s">
         <v>200</v>
       </c>
@@ -3899,13 +3902,13 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="101"/>
-      <c r="B68" s="106"/>
+      <c r="A68" s="98"/>
+      <c r="B68" s="95"/>
       <c r="E68" s="32"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="101"/>
-      <c r="B69" s="94" t="s">
+      <c r="A69" s="98"/>
+      <c r="B69" s="109" t="s">
         <v>305</v>
       </c>
       <c r="C69" s="62" t="s">
@@ -3920,8 +3923,8 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="101"/>
-      <c r="B70" s="95"/>
+      <c r="A70" s="98"/>
+      <c r="B70" s="110"/>
       <c r="C70" s="64" t="s">
         <v>200</v>
       </c>
@@ -3934,16 +3937,16 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="101"/>
-      <c r="B71" s="96"/>
+      <c r="A71" s="98"/>
+      <c r="B71" s="111"/>
       <c r="C71" s="64"/>
       <c r="D71" s="64"/>
       <c r="E71" s="65"/>
       <c r="F71" s="64"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="101"/>
-      <c r="B72" s="91" t="s">
+      <c r="A72" s="98"/>
+      <c r="B72" s="105" t="s">
         <v>6</v>
       </c>
       <c r="C72" s="36" t="s">
@@ -3958,8 +3961,8 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="101"/>
-      <c r="B73" s="97"/>
+      <c r="A73" s="98"/>
+      <c r="B73" s="104"/>
       <c r="C73" s="12" t="s">
         <v>136</v>
       </c>
@@ -3972,8 +3975,8 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="101"/>
-      <c r="B74" s="97"/>
+      <c r="A74" s="98"/>
+      <c r="B74" s="104"/>
       <c r="C74" s="12" t="s">
         <v>152</v>
       </c>
@@ -3986,8 +3989,8 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="101"/>
-      <c r="B75" s="97"/>
+      <c r="A75" s="98"/>
+      <c r="B75" s="104"/>
       <c r="C75" s="12" t="s">
         <v>184</v>
       </c>
@@ -4000,8 +4003,8 @@
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="101"/>
-      <c r="B76" s="97"/>
+      <c r="A76" s="98"/>
+      <c r="B76" s="104"/>
       <c r="C76" s="12" t="s">
         <v>202</v>
       </c>
@@ -4014,8 +4017,8 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="101"/>
-      <c r="B77" s="97"/>
+      <c r="A77" s="98"/>
+      <c r="B77" s="104"/>
       <c r="C77" s="12" t="s">
         <v>210</v>
       </c>
@@ -4028,8 +4031,8 @@
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="101"/>
-      <c r="B78" s="97"/>
+      <c r="A78" s="98"/>
+      <c r="B78" s="104"/>
       <c r="C78" s="12" t="s">
         <v>251</v>
       </c>
@@ -4042,8 +4045,8 @@
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="101"/>
-      <c r="B79" s="97"/>
+      <c r="A79" s="98"/>
+      <c r="B79" s="104"/>
       <c r="C79" s="12" t="s">
         <v>216</v>
       </c>
@@ -4056,8 +4059,8 @@
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="101"/>
-      <c r="B80" s="97"/>
+      <c r="A80" s="98"/>
+      <c r="B80" s="104"/>
       <c r="C80" s="12" t="s">
         <v>241</v>
       </c>
@@ -4070,12 +4073,12 @@
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="101"/>
-      <c r="B81" s="93"/>
+      <c r="A81" s="98"/>
+      <c r="B81" s="108"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="101"/>
-      <c r="B82" s="91" t="s">
+      <c r="A82" s="98"/>
+      <c r="B82" s="105" t="s">
         <v>7</v>
       </c>
       <c r="C82" s="36" t="s">
@@ -4090,8 +4093,8 @@
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="101"/>
-      <c r="B83" s="97"/>
+      <c r="A83" s="98"/>
+      <c r="B83" s="104"/>
       <c r="C83" s="12" t="s">
         <v>137</v>
       </c>
@@ -4104,8 +4107,8 @@
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="101"/>
-      <c r="B84" s="97"/>
+      <c r="A84" s="98"/>
+      <c r="B84" s="104"/>
       <c r="C84" s="12" t="s">
         <v>150</v>
       </c>
@@ -4118,8 +4121,8 @@
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="101"/>
-      <c r="B85" s="97"/>
+      <c r="A85" s="98"/>
+      <c r="B85" s="104"/>
       <c r="C85" s="12" t="s">
         <v>184</v>
       </c>
@@ -4132,8 +4135,8 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="101"/>
-      <c r="B86" s="97"/>
+      <c r="A86" s="98"/>
+      <c r="B86" s="104"/>
       <c r="C86" s="12" t="s">
         <v>202</v>
       </c>
@@ -4146,8 +4149,8 @@
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="101"/>
-      <c r="B87" s="97"/>
+      <c r="A87" s="98"/>
+      <c r="B87" s="104"/>
       <c r="C87" s="12" t="s">
         <v>210</v>
       </c>
@@ -4160,8 +4163,8 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="101"/>
-      <c r="B88" s="97"/>
+      <c r="A88" s="98"/>
+      <c r="B88" s="104"/>
       <c r="C88" s="12" t="s">
         <v>251</v>
       </c>
@@ -4174,8 +4177,8 @@
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="101"/>
-      <c r="B89" s="97"/>
+      <c r="A89" s="98"/>
+      <c r="B89" s="104"/>
       <c r="C89" s="12" t="s">
         <v>216</v>
       </c>
@@ -4188,8 +4191,8 @@
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="101"/>
-      <c r="B90" s="97"/>
+      <c r="A90" s="98"/>
+      <c r="B90" s="104"/>
       <c r="C90" s="12" t="s">
         <v>241</v>
       </c>
@@ -4203,13 +4206,13 @@
     </row>
     <row r="91" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="102"/>
-      <c r="B91" s="98"/>
+      <c r="B91" s="112"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="99" t="s">
+      <c r="A92" s="96" t="s">
         <v>90</v>
       </c>
-      <c r="B92" s="103" t="s">
+      <c r="B92" s="99" t="s">
         <v>87</v>
       </c>
       <c r="C92" s="27" t="s">
@@ -4224,8 +4227,8 @@
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="100"/>
-      <c r="B93" s="104"/>
+      <c r="A93" s="97"/>
+      <c r="B93" s="94"/>
       <c r="C93" s="54" t="s">
         <v>293</v>
       </c>
@@ -4238,8 +4241,8 @@
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="101"/>
-      <c r="B94" s="105"/>
+      <c r="A94" s="98"/>
+      <c r="B94" s="93"/>
       <c r="C94" s="12" t="s">
         <v>196</v>
       </c>
@@ -4252,13 +4255,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="101"/>
-      <c r="B95" s="106"/>
+      <c r="A95" s="98"/>
+      <c r="B95" s="95"/>
       <c r="E95" s="34"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="101"/>
-      <c r="B96" s="107" t="s">
+      <c r="A96" s="98"/>
+      <c r="B96" s="92" t="s">
         <v>93</v>
       </c>
       <c r="C96" s="36" t="s">
@@ -4273,8 +4276,8 @@
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="101"/>
-      <c r="B97" s="105"/>
+      <c r="A97" s="98"/>
+      <c r="B97" s="93"/>
       <c r="C97" s="12" t="s">
         <v>197</v>
       </c>
@@ -4287,16 +4290,16 @@
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="101"/>
-      <c r="B98" s="106"/>
+      <c r="A98" s="98"/>
+      <c r="B98" s="95"/>
       <c r="C98" s="38"/>
       <c r="D98" s="38"/>
       <c r="E98" s="39"/>
       <c r="F98" s="38"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="101"/>
-      <c r="B99" s="107" t="s">
+      <c r="A99" s="98"/>
+      <c r="B99" s="92" t="s">
         <v>94</v>
       </c>
       <c r="C99" s="12" t="s">
@@ -4311,8 +4314,8 @@
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="101"/>
-      <c r="B100" s="105"/>
+      <c r="A100" s="98"/>
+      <c r="B100" s="93"/>
       <c r="C100" s="12" t="s">
         <v>198</v>
       </c>
@@ -4326,17 +4329,17 @@
     </row>
     <row r="101" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="102"/>
-      <c r="B101" s="111"/>
+      <c r="B101" s="106"/>
       <c r="C101" s="42"/>
       <c r="D101" s="42"/>
       <c r="E101" s="43"/>
       <c r="F101" s="42"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="99" t="s">
+      <c r="A102" s="96" t="s">
         <v>212</v>
       </c>
-      <c r="B102" s="103" t="s">
+      <c r="B102" s="99" t="s">
         <v>15</v>
       </c>
       <c r="C102" s="27" t="s">
@@ -4351,8 +4354,8 @@
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="100"/>
-      <c r="B103" s="105"/>
+      <c r="A103" s="97"/>
+      <c r="B103" s="93"/>
       <c r="C103" s="12" t="s">
         <v>225</v>
       </c>
@@ -4364,16 +4367,16 @@
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="100"/>
-      <c r="B104" s="106"/>
+      <c r="A104" s="97"/>
+      <c r="B104" s="95"/>
       <c r="C104" s="38"/>
       <c r="D104" s="38"/>
       <c r="E104" s="38"/>
       <c r="F104" s="38"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="100"/>
-      <c r="B105" s="107" t="s">
+      <c r="A105" s="97"/>
+      <c r="B105" s="92" t="s">
         <v>235</v>
       </c>
       <c r="C105" s="12" t="s">
@@ -4387,8 +4390,8 @@
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="100"/>
-      <c r="B106" s="105"/>
+      <c r="A106" s="97"/>
+      <c r="B106" s="93"/>
       <c r="C106" s="12" t="s">
         <v>233</v>
       </c>
@@ -4400,8 +4403,8 @@
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="100"/>
-      <c r="B107" s="105"/>
+      <c r="A107" s="97"/>
+      <c r="B107" s="93"/>
       <c r="C107" s="12" t="s">
         <v>229</v>
       </c>
@@ -4413,8 +4416,8 @@
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="100"/>
-      <c r="B108" s="105"/>
+      <c r="A108" s="97"/>
+      <c r="B108" s="93"/>
       <c r="C108" s="12" t="s">
         <v>231</v>
       </c>
@@ -4426,8 +4429,8 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="100"/>
-      <c r="B109" s="105"/>
+      <c r="A109" s="97"/>
+      <c r="B109" s="93"/>
       <c r="C109" s="12" t="s">
         <v>234</v>
       </c>
@@ -4439,8 +4442,8 @@
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="100"/>
-      <c r="B110" s="105"/>
+      <c r="A110" s="97"/>
+      <c r="B110" s="93"/>
       <c r="C110" s="12" t="s">
         <v>244</v>
       </c>
@@ -4452,8 +4455,8 @@
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="100"/>
-      <c r="B111" s="107" t="s">
+      <c r="A111" s="97"/>
+      <c r="B111" s="92" t="s">
         <v>265</v>
       </c>
       <c r="C111" s="36" t="s">
@@ -4468,8 +4471,8 @@
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="100"/>
-      <c r="B112" s="104"/>
+      <c r="A112" s="97"/>
+      <c r="B112" s="94"/>
       <c r="C112" s="54" t="s">
         <v>261</v>
       </c>
@@ -4482,8 +4485,8 @@
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="100"/>
-      <c r="B113" s="104"/>
+      <c r="A113" s="97"/>
+      <c r="B113" s="94"/>
       <c r="C113" s="54" t="s">
         <v>276</v>
       </c>
@@ -4496,8 +4499,8 @@
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="100"/>
-      <c r="B114" s="104"/>
+      <c r="A114" s="97"/>
+      <c r="B114" s="94"/>
       <c r="C114" s="54" t="s">
         <v>262</v>
       </c>
@@ -4510,8 +4513,8 @@
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="100"/>
-      <c r="B115" s="104"/>
+      <c r="A115" s="97"/>
+      <c r="B115" s="94"/>
       <c r="C115" s="54" t="s">
         <v>278</v>
       </c>
@@ -4524,8 +4527,8 @@
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="100"/>
-      <c r="B116" s="104"/>
+      <c r="A116" s="97"/>
+      <c r="B116" s="94"/>
       <c r="C116" s="54" t="s">
         <v>282</v>
       </c>
@@ -4538,22 +4541,22 @@
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="100"/>
-      <c r="B117" s="104"/>
-      <c r="C117" s="112" t="s">
+      <c r="A117" s="97"/>
+      <c r="B117" s="94"/>
+      <c r="C117" s="74" t="s">
         <v>332</v>
       </c>
-      <c r="D117" s="112" t="s">
+      <c r="D117" s="74" t="s">
         <v>331</v>
       </c>
-      <c r="E117" s="112"/>
-      <c r="F117" s="112" t="s">
+      <c r="E117" s="74"/>
+      <c r="F117" s="74" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="100"/>
-      <c r="B118" s="104"/>
+      <c r="A118" s="97"/>
+      <c r="B118" s="94"/>
       <c r="C118" s="54" t="s">
         <v>259</v>
       </c>
@@ -4566,8 +4569,8 @@
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="100"/>
-      <c r="B119" s="104"/>
+      <c r="A119" s="97"/>
+      <c r="B119" s="94"/>
       <c r="C119" s="54" t="s">
         <v>263</v>
       </c>
@@ -4580,8 +4583,8 @@
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="100"/>
-      <c r="B120" s="104"/>
+      <c r="A120" s="97"/>
+      <c r="B120" s="94"/>
       <c r="C120" s="54" t="s">
         <v>264</v>
       </c>
@@ -4594,8 +4597,8 @@
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="100"/>
-      <c r="B121" s="107" t="s">
+      <c r="A121" s="97"/>
+      <c r="B121" s="92" t="s">
         <v>283</v>
       </c>
       <c r="C121" s="36" t="s">
@@ -4610,8 +4613,8 @@
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="100"/>
-      <c r="B122" s="104"/>
+      <c r="A122" s="97"/>
+      <c r="B122" s="94"/>
       <c r="C122" s="54" t="s">
         <v>286</v>
       </c>
@@ -4624,8 +4627,8 @@
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="100"/>
-      <c r="B123" s="104"/>
+      <c r="A123" s="97"/>
+      <c r="B123" s="94"/>
       <c r="C123" s="54" t="s">
         <v>288</v>
       </c>
@@ -4638,8 +4641,8 @@
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="100"/>
-      <c r="B124" s="104"/>
+      <c r="A124" s="97"/>
+      <c r="B124" s="94"/>
       <c r="C124" s="12" t="s">
         <v>289</v>
       </c>
@@ -4651,12 +4654,12 @@
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="100"/>
-      <c r="B125" s="106"/>
+      <c r="A125" s="97"/>
+      <c r="B125" s="95"/>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="100"/>
-      <c r="B126" s="107" t="s">
+      <c r="A126" s="97"/>
+      <c r="B126" s="92" t="s">
         <v>294</v>
       </c>
       <c r="C126" s="36" t="s">
@@ -4671,8 +4674,8 @@
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="100"/>
-      <c r="B127" s="105"/>
+      <c r="A127" s="97"/>
+      <c r="B127" s="93"/>
       <c r="C127" s="12" t="s">
         <v>297</v>
       </c>
@@ -4684,10 +4687,17 @@
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="100"/>
+      <c r="A128" s="97"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="B23:B32"/>
+    <mergeCell ref="B69:B71"/>
+    <mergeCell ref="B72:B81"/>
+    <mergeCell ref="B82:B91"/>
+    <mergeCell ref="A92:A101"/>
+    <mergeCell ref="B92:B95"/>
+    <mergeCell ref="B96:B98"/>
     <mergeCell ref="B126:B127"/>
     <mergeCell ref="B121:B125"/>
     <mergeCell ref="A102:A128"/>
@@ -4704,13 +4714,6 @@
     <mergeCell ref="B111:B120"/>
     <mergeCell ref="B102:B104"/>
     <mergeCell ref="A66:A91"/>
-    <mergeCell ref="B23:B32"/>
-    <mergeCell ref="B69:B71"/>
-    <mergeCell ref="B72:B81"/>
-    <mergeCell ref="B82:B91"/>
-    <mergeCell ref="A92:A101"/>
-    <mergeCell ref="B92:B95"/>
-    <mergeCell ref="B96:B98"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
